--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -2126,10 +2126,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130360394</v>
+        <v>130360384</v>
       </c>
       <c r="B17" t="n">
-        <v>80285</v>
+        <v>91679</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2137,21 +2137,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462876</v>
+        <v>463252</v>
       </c>
       <c r="R17" t="n">
-        <v>6992460</v>
+        <v>6992494</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130360384</v>
+        <v>130360394</v>
       </c>
       <c r="B18" t="n">
-        <v>91679</v>
+        <v>80285</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463252</v>
+        <v>462876</v>
       </c>
       <c r="R18" t="n">
-        <v>6992494</v>
+        <v>6992460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130360393</v>
       </c>
       <c r="B2" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130360395</v>
       </c>
       <c r="B3" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130360397</v>
       </c>
       <c r="B4" t="n">
-        <v>83158</v>
+        <v>83161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130360385</v>
       </c>
       <c r="B5" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130360386</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130360399</v>
       </c>
       <c r="B7" t="n">
-        <v>92451</v>
+        <v>92454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130360382</v>
       </c>
       <c r="B8" t="n">
-        <v>80286</v>
+        <v>80289</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>130360387</v>
       </c>
       <c r="B9" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>130360391</v>
       </c>
       <c r="B10" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>130360398</v>
       </c>
       <c r="B11" t="n">
-        <v>83158</v>
+        <v>83161</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>130360392</v>
       </c>
       <c r="B12" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>130360388</v>
       </c>
       <c r="B13" t="n">
-        <v>78192</v>
+        <v>78195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>130360390</v>
       </c>
       <c r="B14" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>130360389</v>
       </c>
       <c r="B15" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>130360383</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>130360384</v>
       </c>
       <c r="B17" t="n">
-        <v>91679</v>
+        <v>91682</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>130360394</v>
       </c>
       <c r="B18" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130360393</v>
       </c>
       <c r="B2" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130360395</v>
       </c>
       <c r="B3" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130360397</v>
       </c>
       <c r="B4" t="n">
-        <v>83161</v>
+        <v>83187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130360385</v>
       </c>
       <c r="B5" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130360386</v>
       </c>
       <c r="B6" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130360399</v>
       </c>
       <c r="B7" t="n">
-        <v>92454</v>
+        <v>92480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130360382</v>
       </c>
       <c r="B8" t="n">
-        <v>80289</v>
+        <v>80315</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>130360387</v>
       </c>
       <c r="B9" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>130360391</v>
       </c>
       <c r="B10" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>130360398</v>
       </c>
       <c r="B11" t="n">
-        <v>83161</v>
+        <v>83187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>130360392</v>
       </c>
       <c r="B12" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>130360388</v>
       </c>
       <c r="B13" t="n">
-        <v>78195</v>
+        <v>78221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>130360390</v>
       </c>
       <c r="B14" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>130360389</v>
       </c>
       <c r="B15" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>130360383</v>
       </c>
       <c r="B16" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>130360384</v>
       </c>
       <c r="B17" t="n">
-        <v>91682</v>
+        <v>91708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>130360394</v>
       </c>
       <c r="B18" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>130360397</v>
       </c>
       <c r="B4" t="n">
-        <v>83187</v>
+        <v>83188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130360385</v>
+        <v>130360386</v>
       </c>
       <c r="B5" t="n">
-        <v>91757</v>
+        <v>98950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463108</v>
+        <v>463100</v>
       </c>
       <c r="R5" t="n">
-        <v>6992442</v>
+        <v>6992447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130360386</v>
+        <v>130360385</v>
       </c>
       <c r="B6" t="n">
-        <v>98949</v>
+        <v>91758</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463100</v>
+        <v>463108</v>
       </c>
       <c r="R6" t="n">
-        <v>6992447</v>
+        <v>6992442</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>130360399</v>
       </c>
       <c r="B7" t="n">
-        <v>92480</v>
+        <v>92481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>130360387</v>
       </c>
       <c r="B9" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,10 +1447,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130360391</v>
+        <v>130360398</v>
       </c>
       <c r="B10" t="n">
-        <v>80314</v>
+        <v>83188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463269</v>
+        <v>463284</v>
       </c>
       <c r="R10" t="n">
-        <v>6992435</v>
+        <v>6992372</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130360398</v>
+        <v>130360391</v>
       </c>
       <c r="B11" t="n">
-        <v>83187</v>
+        <v>80314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463284</v>
+        <v>463269</v>
       </c>
       <c r="R11" t="n">
-        <v>6992372</v>
+        <v>6992435</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
         <v>130360384</v>
       </c>
       <c r="B17" t="n">
-        <v>91708</v>
+        <v>91709</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>130360397</v>
       </c>
       <c r="B4" t="n">
-        <v>83188</v>
+        <v>83189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130360386</v>
       </c>
       <c r="B5" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130360385</v>
       </c>
       <c r="B6" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130360399</v>
       </c>
       <c r="B7" t="n">
-        <v>92481</v>
+        <v>92482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>130360387</v>
       </c>
       <c r="B9" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,10 +1447,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130360398</v>
+        <v>130360391</v>
       </c>
       <c r="B10" t="n">
-        <v>83188</v>
+        <v>80314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463284</v>
+        <v>463269</v>
       </c>
       <c r="R10" t="n">
-        <v>6992372</v>
+        <v>6992435</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130360391</v>
+        <v>130360398</v>
       </c>
       <c r="B11" t="n">
-        <v>80314</v>
+        <v>83189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463269</v>
+        <v>463284</v>
       </c>
       <c r="R11" t="n">
-        <v>6992435</v>
+        <v>6992372</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130360384</v>
+        <v>130360394</v>
       </c>
       <c r="B17" t="n">
-        <v>91709</v>
+        <v>80314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2137,21 +2137,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463252</v>
+        <v>462876</v>
       </c>
       <c r="R17" t="n">
-        <v>6992494</v>
+        <v>6992460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130360394</v>
+        <v>130360384</v>
       </c>
       <c r="B18" t="n">
-        <v>80314</v>
+        <v>91710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462876</v>
+        <v>463252</v>
       </c>
       <c r="R18" t="n">
-        <v>6992460</v>
+        <v>6992494</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130360393</v>
       </c>
       <c r="B2" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130360395</v>
       </c>
       <c r="B3" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130360397</v>
       </c>
       <c r="B4" t="n">
-        <v>83189</v>
+        <v>83191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130360386</v>
       </c>
       <c r="B5" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130360385</v>
       </c>
       <c r="B6" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130360399</v>
       </c>
       <c r="B7" t="n">
-        <v>92482</v>
+        <v>92484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130360382</v>
       </c>
       <c r="B8" t="n">
-        <v>80315</v>
+        <v>80317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>130360387</v>
       </c>
       <c r="B9" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>130360391</v>
       </c>
       <c r="B10" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>130360398</v>
       </c>
       <c r="B11" t="n">
-        <v>83189</v>
+        <v>83191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>130360392</v>
       </c>
       <c r="B12" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>130360388</v>
       </c>
       <c r="B13" t="n">
-        <v>78221</v>
+        <v>78223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>130360390</v>
       </c>
       <c r="B14" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>130360389</v>
       </c>
       <c r="B15" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>130360383</v>
       </c>
       <c r="B16" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>130360394</v>
       </c>
       <c r="B17" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>130360384</v>
       </c>
       <c r="B18" t="n">
-        <v>91710</v>
+        <v>91712</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130360386</v>
+        <v>130360385</v>
       </c>
       <c r="B5" t="n">
-        <v>98953</v>
+        <v>91761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463100</v>
+        <v>463108</v>
       </c>
       <c r="R5" t="n">
-        <v>6992447</v>
+        <v>6992442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130360385</v>
+        <v>130360386</v>
       </c>
       <c r="B6" t="n">
-        <v>91761</v>
+        <v>98957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463108</v>
+        <v>463100</v>
       </c>
       <c r="R6" t="n">
-        <v>6992442</v>
+        <v>6992447</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>130360399</v>
       </c>
       <c r="B7" t="n">
-        <v>92484</v>
+        <v>92488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130360394</v>
+        <v>130360384</v>
       </c>
       <c r="B17" t="n">
-        <v>80316</v>
+        <v>91712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2137,21 +2137,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462876</v>
+        <v>463252</v>
       </c>
       <c r="R17" t="n">
-        <v>6992460</v>
+        <v>6992494</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130360384</v>
+        <v>130360394</v>
       </c>
       <c r="B18" t="n">
-        <v>91712</v>
+        <v>80316</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463252</v>
+        <v>462876</v>
       </c>
       <c r="R18" t="n">
-        <v>6992494</v>
+        <v>6992460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130360382</v>
+        <v>130360387</v>
       </c>
       <c r="B8" t="n">
-        <v>80317</v>
+        <v>91781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,23 +1268,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1292,10 +1288,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462746</v>
+        <v>462765</v>
       </c>
       <c r="R8" t="n">
-        <v>6992588</v>
+        <v>6992487</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1350,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130360387</v>
+        <v>130360382</v>
       </c>
       <c r="B9" t="n">
-        <v>91781</v>
+        <v>80317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,19 +1361,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462765</v>
+        <v>462746</v>
       </c>
       <c r="R9" t="n">
-        <v>6992487</v>
+        <v>6992588</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130360387</v>
+        <v>130360382</v>
       </c>
       <c r="B8" t="n">
-        <v>91781</v>
+        <v>80317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,19 +1268,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1288,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462765</v>
+        <v>462746</v>
       </c>
       <c r="R8" t="n">
-        <v>6992487</v>
+        <v>6992588</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130360382</v>
+        <v>130360387</v>
       </c>
       <c r="B9" t="n">
-        <v>80317</v>
+        <v>91781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1361,23 +1365,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462746</v>
+        <v>462765</v>
       </c>
       <c r="R9" t="n">
-        <v>6992588</v>
+        <v>6992487</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130360384</v>
+        <v>130360394</v>
       </c>
       <c r="B17" t="n">
-        <v>91712</v>
+        <v>80316</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2137,21 +2137,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463252</v>
+        <v>462876</v>
       </c>
       <c r="R17" t="n">
-        <v>6992494</v>
+        <v>6992460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130360394</v>
+        <v>130360384</v>
       </c>
       <c r="B18" t="n">
-        <v>80316</v>
+        <v>91712</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462876</v>
+        <v>463252</v>
       </c>
       <c r="R18" t="n">
-        <v>6992460</v>
+        <v>6992494</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130360385</v>
+        <v>130360386</v>
       </c>
       <c r="B5" t="n">
-        <v>91761</v>
+        <v>98957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463108</v>
+        <v>463100</v>
       </c>
       <c r="R5" t="n">
-        <v>6992442</v>
+        <v>6992447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130360386</v>
+        <v>130360385</v>
       </c>
       <c r="B6" t="n">
-        <v>98957</v>
+        <v>91761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463100</v>
+        <v>463108</v>
       </c>
       <c r="R6" t="n">
-        <v>6992447</v>
+        <v>6992442</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130360394</v>
+        <v>130360384</v>
       </c>
       <c r="B17" t="n">
-        <v>80316</v>
+        <v>91712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2137,21 +2137,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462876</v>
+        <v>463252</v>
       </c>
       <c r="R17" t="n">
-        <v>6992460</v>
+        <v>6992494</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130360384</v>
+        <v>130360394</v>
       </c>
       <c r="B18" t="n">
-        <v>91712</v>
+        <v>80316</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463252</v>
+        <v>462876</v>
       </c>
       <c r="R18" t="n">
-        <v>6992494</v>
+        <v>6992460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130360393</v>
       </c>
       <c r="B2" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130360395</v>
       </c>
       <c r="B3" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130360397</v>
       </c>
       <c r="B4" t="n">
-        <v>83191</v>
+        <v>83199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130360386</v>
+        <v>130360385</v>
       </c>
       <c r="B5" t="n">
-        <v>98957</v>
+        <v>91774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463100</v>
+        <v>463108</v>
       </c>
       <c r="R5" t="n">
-        <v>6992447</v>
+        <v>6992442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130360385</v>
+        <v>130360386</v>
       </c>
       <c r="B6" t="n">
-        <v>91761</v>
+        <v>98970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463108</v>
+        <v>463100</v>
       </c>
       <c r="R6" t="n">
-        <v>6992442</v>
+        <v>6992447</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>130360399</v>
       </c>
       <c r="B7" t="n">
-        <v>92488</v>
+        <v>92501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130360382</v>
       </c>
       <c r="B8" t="n">
-        <v>80317</v>
+        <v>80325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>130360387</v>
       </c>
       <c r="B9" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,10 +1447,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130360391</v>
+        <v>130360398</v>
       </c>
       <c r="B10" t="n">
-        <v>80316</v>
+        <v>83199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463269</v>
+        <v>463284</v>
       </c>
       <c r="R10" t="n">
-        <v>6992435</v>
+        <v>6992372</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130360398</v>
+        <v>130360391</v>
       </c>
       <c r="B11" t="n">
-        <v>83191</v>
+        <v>80324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463284</v>
+        <v>463269</v>
       </c>
       <c r="R11" t="n">
-        <v>6992372</v>
+        <v>6992435</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1644,7 +1644,7 @@
         <v>130360392</v>
       </c>
       <c r="B12" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>130360388</v>
       </c>
       <c r="B13" t="n">
-        <v>78223</v>
+        <v>78231</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>130360390</v>
       </c>
       <c r="B14" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>130360389</v>
       </c>
       <c r="B15" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>130360383</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130360384</v>
+        <v>130360394</v>
       </c>
       <c r="B17" t="n">
-        <v>91712</v>
+        <v>80324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2137,21 +2137,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463252</v>
+        <v>462876</v>
       </c>
       <c r="R17" t="n">
-        <v>6992494</v>
+        <v>6992460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130360394</v>
+        <v>130360384</v>
       </c>
       <c r="B18" t="n">
-        <v>80316</v>
+        <v>91724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462876</v>
+        <v>463252</v>
       </c>
       <c r="R18" t="n">
-        <v>6992460</v>
+        <v>6992494</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130360393</v>
       </c>
       <c r="B2" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130360395</v>
       </c>
       <c r="B3" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130360397</v>
       </c>
       <c r="B4" t="n">
-        <v>83199</v>
+        <v>83200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130360385</v>
+        <v>130360386</v>
       </c>
       <c r="B5" t="n">
-        <v>91774</v>
+        <v>98971</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463108</v>
+        <v>463100</v>
       </c>
       <c r="R5" t="n">
-        <v>6992442</v>
+        <v>6992447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130360386</v>
+        <v>130360385</v>
       </c>
       <c r="B6" t="n">
-        <v>98970</v>
+        <v>91775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463100</v>
+        <v>463108</v>
       </c>
       <c r="R6" t="n">
-        <v>6992447</v>
+        <v>6992442</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>130360399</v>
       </c>
       <c r="B7" t="n">
-        <v>92501</v>
+        <v>92502</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130360382</v>
+        <v>130360387</v>
       </c>
       <c r="B8" t="n">
-        <v>80325</v>
+        <v>91795</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,23 +1268,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1292,10 +1288,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462746</v>
+        <v>462765</v>
       </c>
       <c r="R8" t="n">
-        <v>6992588</v>
+        <v>6992487</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1350,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130360387</v>
+        <v>130360382</v>
       </c>
       <c r="B9" t="n">
-        <v>91794</v>
+        <v>80326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,19 +1361,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462765</v>
+        <v>462746</v>
       </c>
       <c r="R9" t="n">
-        <v>6992487</v>
+        <v>6992588</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1447,10 +1447,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130360398</v>
+        <v>130360391</v>
       </c>
       <c r="B10" t="n">
-        <v>83199</v>
+        <v>80325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463284</v>
+        <v>463269</v>
       </c>
       <c r="R10" t="n">
-        <v>6992372</v>
+        <v>6992435</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130360391</v>
+        <v>130360398</v>
       </c>
       <c r="B11" t="n">
-        <v>80324</v>
+        <v>83200</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463269</v>
+        <v>463284</v>
       </c>
       <c r="R11" t="n">
-        <v>6992435</v>
+        <v>6992372</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1644,7 +1644,7 @@
         <v>130360392</v>
       </c>
       <c r="B12" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>130360388</v>
       </c>
       <c r="B13" t="n">
-        <v>78231</v>
+        <v>78232</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>130360390</v>
       </c>
       <c r="B14" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>130360389</v>
       </c>
       <c r="B15" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>130360383</v>
       </c>
       <c r="B16" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>130360394</v>
       </c>
       <c r="B17" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>130360384</v>
       </c>
       <c r="B18" t="n">
-        <v>91724</v>
+        <v>91725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130360393</v>
       </c>
       <c r="B2" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130360395</v>
       </c>
       <c r="B3" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130360397</v>
       </c>
       <c r="B4" t="n">
-        <v>83200</v>
+        <v>83201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130360386</v>
       </c>
       <c r="B5" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130360385</v>
       </c>
       <c r="B6" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130360399</v>
       </c>
       <c r="B7" t="n">
-        <v>92502</v>
+        <v>92503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130360387</v>
       </c>
       <c r="B8" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>130360382</v>
       </c>
       <c r="B9" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>130360391</v>
       </c>
       <c r="B10" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>130360398</v>
       </c>
       <c r="B11" t="n">
-        <v>83200</v>
+        <v>83201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>130360392</v>
       </c>
       <c r="B12" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>130360388</v>
       </c>
       <c r="B13" t="n">
-        <v>78232</v>
+        <v>78233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>130360390</v>
       </c>
       <c r="B14" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>130360389</v>
       </c>
       <c r="B15" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>130360383</v>
       </c>
       <c r="B16" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130360394</v>
+        <v>130360384</v>
       </c>
       <c r="B17" t="n">
-        <v>80325</v>
+        <v>91726</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2137,21 +2137,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462876</v>
+        <v>463252</v>
       </c>
       <c r="R17" t="n">
-        <v>6992460</v>
+        <v>6992494</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130360384</v>
+        <v>130360394</v>
       </c>
       <c r="B18" t="n">
-        <v>91725</v>
+        <v>80326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463252</v>
+        <v>462876</v>
       </c>
       <c r="R18" t="n">
-        <v>6992494</v>
+        <v>6992460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130360386</v>
+        <v>130360385</v>
       </c>
       <c r="B5" t="n">
-        <v>98974</v>
+        <v>91776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463100</v>
+        <v>463108</v>
       </c>
       <c r="R5" t="n">
-        <v>6992447</v>
+        <v>6992442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130360385</v>
+        <v>130360386</v>
       </c>
       <c r="B6" t="n">
-        <v>91776</v>
+        <v>98974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463108</v>
+        <v>463100</v>
       </c>
       <c r="R6" t="n">
-        <v>6992442</v>
+        <v>6992447</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130360387</v>
+        <v>130360382</v>
       </c>
       <c r="B8" t="n">
-        <v>91796</v>
+        <v>80327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,19 +1268,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1288,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462765</v>
+        <v>462746</v>
       </c>
       <c r="R8" t="n">
-        <v>6992487</v>
+        <v>6992588</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130360382</v>
+        <v>130360387</v>
       </c>
       <c r="B9" t="n">
-        <v>80327</v>
+        <v>91796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1361,23 +1365,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462746</v>
+        <v>462765</v>
       </c>
       <c r="R9" t="n">
-        <v>6992588</v>
+        <v>6992487</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130360382</v>
+        <v>130360387</v>
       </c>
       <c r="B8" t="n">
-        <v>80327</v>
+        <v>91796</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,23 +1268,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1292,10 +1288,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462746</v>
+        <v>462765</v>
       </c>
       <c r="R8" t="n">
-        <v>6992588</v>
+        <v>6992487</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1350,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130360387</v>
+        <v>130360382</v>
       </c>
       <c r="B9" t="n">
-        <v>91796</v>
+        <v>80327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,19 +1361,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462765</v>
+        <v>462746</v>
       </c>
       <c r="R9" t="n">
-        <v>6992487</v>
+        <v>6992588</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130360384</v>
+        <v>130360394</v>
       </c>
       <c r="B17" t="n">
-        <v>91726</v>
+        <v>80326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2137,21 +2137,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463252</v>
+        <v>462876</v>
       </c>
       <c r="R17" t="n">
-        <v>6992494</v>
+        <v>6992460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130360394</v>
+        <v>130360384</v>
       </c>
       <c r="B18" t="n">
-        <v>80326</v>
+        <v>91726</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462876</v>
+        <v>463252</v>
       </c>
       <c r="R18" t="n">
-        <v>6992460</v>
+        <v>6992494</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -2126,10 +2126,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130360394</v>
+        <v>130360384</v>
       </c>
       <c r="B17" t="n">
-        <v>80326</v>
+        <v>91726</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2137,21 +2137,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462876</v>
+        <v>463252</v>
       </c>
       <c r="R17" t="n">
-        <v>6992460</v>
+        <v>6992494</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130360384</v>
+        <v>130360394</v>
       </c>
       <c r="B18" t="n">
-        <v>91726</v>
+        <v>80326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463252</v>
+        <v>462876</v>
       </c>
       <c r="R18" t="n">
-        <v>6992494</v>
+        <v>6992460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130360385</v>
+        <v>130360386</v>
       </c>
       <c r="B5" t="n">
-        <v>91776</v>
+        <v>98974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463108</v>
+        <v>463100</v>
       </c>
       <c r="R5" t="n">
-        <v>6992442</v>
+        <v>6992447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130360386</v>
+        <v>130360385</v>
       </c>
       <c r="B6" t="n">
-        <v>98974</v>
+        <v>91776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463100</v>
+        <v>463108</v>
       </c>
       <c r="R6" t="n">
-        <v>6992447</v>
+        <v>6992442</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130360387</v>
+        <v>130360382</v>
       </c>
       <c r="B8" t="n">
-        <v>91796</v>
+        <v>80327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,19 +1268,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1288,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462765</v>
+        <v>462746</v>
       </c>
       <c r="R8" t="n">
-        <v>6992487</v>
+        <v>6992588</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130360382</v>
+        <v>130360387</v>
       </c>
       <c r="B9" t="n">
-        <v>80327</v>
+        <v>91796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1361,23 +1365,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462746</v>
+        <v>462765</v>
       </c>
       <c r="R9" t="n">
-        <v>6992588</v>
+        <v>6992487</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>130360386</v>
       </c>
       <c r="B5" t="n">
-        <v>98974</v>
+        <v>98988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130360385</v>
       </c>
       <c r="B6" t="n">
-        <v>91776</v>
+        <v>91784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130360399</v>
       </c>
       <c r="B7" t="n">
-        <v>92503</v>
+        <v>92511</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130360382</v>
+        <v>130360387</v>
       </c>
       <c r="B8" t="n">
-        <v>80327</v>
+        <v>91804</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,23 +1268,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1292,10 +1288,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462746</v>
+        <v>462765</v>
       </c>
       <c r="R8" t="n">
-        <v>6992588</v>
+        <v>6992487</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1350,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130360387</v>
+        <v>130360382</v>
       </c>
       <c r="B9" t="n">
-        <v>91796</v>
+        <v>80327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,19 +1361,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462765</v>
+        <v>462746</v>
       </c>
       <c r="R9" t="n">
-        <v>6992487</v>
+        <v>6992588</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
         <v>130360384</v>
       </c>
       <c r="B17" t="n">
-        <v>91726</v>
+        <v>91734</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -5321,7 +5321,7 @@
         <v>131703248</v>
       </c>
       <c r="B42" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5444,10 +5444,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131703240</v>
+        <v>131703255</v>
       </c>
       <c r="B43" t="n">
-        <v>91889</v>
+        <v>80422</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5455,28 +5455,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5486,10 +5486,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>463186</v>
+        <v>463239</v>
       </c>
       <c r="R43" t="n">
-        <v>6992482</v>
+        <v>6992280</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5524,6 +5524,11 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apothecier på en sälg.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5541,22 +5546,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5574,10 +5579,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131703255</v>
+        <v>131703240</v>
       </c>
       <c r="B44" t="n">
-        <v>80420</v>
+        <v>91892</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5585,28 +5590,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5616,10 +5621,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>463239</v>
+        <v>463186</v>
       </c>
       <c r="R44" t="n">
-        <v>6992280</v>
+        <v>6992482</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5654,11 +5659,6 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Fertil lunglav med apothecier på en sälg.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5676,22 +5676,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5712,7 +5712,7 @@
         <v>131703261</v>
       </c>
       <c r="B45" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>131703266</v>
       </c>
       <c r="B46" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>131703251</v>
       </c>
       <c r="B47" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>131703245</v>
       </c>
       <c r="B48" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6215,10 +6215,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131703247</v>
+        <v>131703267</v>
       </c>
       <c r="B49" t="n">
-        <v>80420</v>
+        <v>91912</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6226,26 +6226,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>463310</v>
+        <v>463144</v>
       </c>
       <c r="R49" t="n">
-        <v>6992618</v>
+        <v>6992498</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6291,6 +6291,11 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Fruktkroppar i en liggande död gran.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6308,22 +6313,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6344,7 +6349,7 @@
         <v>131703263</v>
       </c>
       <c r="B50" t="n">
-        <v>91885</v>
+        <v>91888</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6466,10 +6471,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131703267</v>
+        <v>131703247</v>
       </c>
       <c r="B51" t="n">
-        <v>91909</v>
+        <v>80422</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6477,26 +6482,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6504,10 +6509,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>463144</v>
+        <v>463310</v>
       </c>
       <c r="R51" t="n">
-        <v>6992498</v>
+        <v>6992618</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6542,11 +6547,6 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Fruktkroppar i en liggande död gran.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6564,22 +6564,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6600,7 +6600,7 @@
         <v>131703252</v>
       </c>
       <c r="B52" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>131703257</v>
       </c>
       <c r="B53" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>131703268</v>
       </c>
       <c r="B54" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>131703249</v>
       </c>
       <c r="B55" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>131703239</v>
       </c>
       <c r="B56" t="n">
-        <v>83295</v>
+        <v>83297</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>131703269</v>
       </c>
       <c r="B57" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>131703260</v>
       </c>
       <c r="B58" t="n">
-        <v>78327</v>
+        <v>78329</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>131703243</v>
       </c>
       <c r="B59" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>131703262</v>
       </c>
       <c r="B60" t="n">
-        <v>91885</v>
+        <v>91888</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>131703264</v>
       </c>
       <c r="B61" t="n">
-        <v>91885</v>
+        <v>91888</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>131703253</v>
       </c>
       <c r="B62" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>131703256</v>
       </c>
       <c r="B63" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>131703246</v>
       </c>
       <c r="B64" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>131703254</v>
       </c>
       <c r="B65" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>131703259</v>
       </c>
       <c r="B66" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>131703250</v>
       </c>
       <c r="B67" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>131703244</v>
       </c>
       <c r="B68" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8752,10 +8752,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131703258</v>
+        <v>131703270</v>
       </c>
       <c r="B69" t="n">
-        <v>80420</v>
+        <v>83163</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8763,21 +8763,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8790,10 +8790,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>463161</v>
+        <v>463157</v>
       </c>
       <c r="R69" t="n">
-        <v>6992400</v>
+        <v>6992429</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8843,24 +8843,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog.</t>
+        </is>
+      </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8878,10 +8878,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131703270</v>
+        <v>131703258</v>
       </c>
       <c r="B70" t="n">
-        <v>83161</v>
+        <v>80422</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8889,21 +8889,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8916,10 +8916,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>463157</v>
+        <v>463161</v>
       </c>
       <c r="R70" t="n">
-        <v>6992429</v>
+        <v>6992400</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8969,24 +8969,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog.</t>
-        </is>
-      </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9270,7 +9270,7 @@
         <v>131703265</v>
       </c>
       <c r="B73" t="n">
-        <v>91885</v>
+        <v>91888</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -6980,10 +6980,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131703249</v>
+        <v>131703239</v>
       </c>
       <c r="B55" t="n">
-        <v>80422</v>
+        <v>83297</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6991,21 +6991,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>463272</v>
+        <v>463161</v>
       </c>
       <c r="R55" t="n">
-        <v>6992511</v>
+        <v>6992394</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7073,22 +7073,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7106,10 +7101,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131703239</v>
+        <v>131703249</v>
       </c>
       <c r="B56" t="n">
-        <v>83297</v>
+        <v>80422</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7117,21 +7112,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7144,10 +7139,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>463161</v>
+        <v>463272</v>
       </c>
       <c r="R56" t="n">
-        <v>6992394</v>
+        <v>6992511</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7199,17 +7194,22 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130360393</v>
+        <v>130360399</v>
       </c>
       <c r="B2" t="n">
-        <v>80326</v>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463223</v>
+        <v>463044</v>
       </c>
       <c r="R2" t="n">
-        <v>6992479</v>
+        <v>6992413</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130360395</v>
+        <v>130360384</v>
       </c>
       <c r="B3" t="n">
-        <v>80326</v>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462873</v>
+        <v>463252</v>
       </c>
       <c r="R3" t="n">
-        <v>6992482</v>
+        <v>6992494</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130360397</v>
+        <v>131703262</v>
       </c>
       <c r="B4" t="n">
-        <v>83201</v>
+        <v>91970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rörbodarna, Jmt</t>
+          <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463272</v>
+        <v>463229</v>
       </c>
       <c r="R4" t="n">
-        <v>6992492</v>
+        <v>6992394</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +941,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -948,63 +955,91 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130360386</v>
+        <v>131703263</v>
       </c>
       <c r="B5" t="n">
-        <v>98988</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rörbodarna, Jmt</t>
+          <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463100</v>
+        <v>463359</v>
       </c>
       <c r="R5" t="n">
-        <v>6992447</v>
+        <v>6992212</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1045,28 +1080,49 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130360385</v>
+        <v>131703264</v>
       </c>
       <c r="B6" t="n">
-        <v>91784</v>
+        <v>91970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1130,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rörbodarna, Jmt</t>
+          <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463108</v>
+        <v>463196</v>
       </c>
       <c r="R6" t="n">
-        <v>6992442</v>
+        <v>6992334</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1142,63 +1205,91 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130360399</v>
+        <v>131703265</v>
       </c>
       <c r="B7" t="n">
-        <v>92511</v>
+        <v>91970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörbodarna, Jmt</t>
+          <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463044</v>
+        <v>463389</v>
       </c>
       <c r="R7" t="n">
-        <v>6992413</v>
+        <v>6992233</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1316,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1239,28 +1330,49 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130360387</v>
+        <v>130360385</v>
       </c>
       <c r="B8" t="n">
-        <v>91804</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,19 +1380,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1288,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462765</v>
+        <v>463108</v>
       </c>
       <c r="R8" t="n">
-        <v>6992487</v>
+        <v>6992442</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130360382</v>
+        <v>131703240</v>
       </c>
       <c r="B9" t="n">
-        <v>80327</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1361,34 +1477,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rörbodarna, Jmt</t>
+          <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462746</v>
+        <v>463186</v>
       </c>
       <c r="R9" t="n">
-        <v>6992588</v>
+        <v>6992482</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1415,12 +1538,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1429,28 +1552,54 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130360391</v>
+        <v>131703270</v>
       </c>
       <c r="B10" t="n">
-        <v>80326</v>
+        <v>83222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,34 +1607,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rörbodarna, Jmt</t>
+          <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463269</v>
+        <v>463157</v>
       </c>
       <c r="R10" t="n">
-        <v>6992435</v>
+        <v>6992429</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1512,12 +1664,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1526,28 +1678,54 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130360398</v>
+        <v>130360382</v>
       </c>
       <c r="B11" t="n">
-        <v>83201</v>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1555,21 +1733,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1757,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463284</v>
+        <v>462746</v>
       </c>
       <c r="R11" t="n">
-        <v>6992372</v>
+        <v>6992588</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,45 +1819,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130360392</v>
+        <v>131676381</v>
       </c>
       <c r="B12" t="n">
-        <v>80326</v>
+        <v>96410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2812</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rörbodarna, Jmt</t>
+          <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463260</v>
+        <v>463304</v>
       </c>
       <c r="R12" t="n">
-        <v>6992442</v>
+        <v>6992512</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1706,12 +1888,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1720,63 +1902,73 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130360388</v>
+        <v>131676382</v>
       </c>
       <c r="B13" t="n">
-        <v>78233</v>
+        <v>96410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>2812</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rörbodarna, Jmt</t>
+          <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463285</v>
+        <v>463288</v>
       </c>
       <c r="R13" t="n">
-        <v>6992372</v>
+        <v>6992341</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1803,12 +1995,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1817,63 +2009,78 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med en del klena träd.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130360390</v>
+        <v>131676383</v>
       </c>
       <c r="B14" t="n">
-        <v>80326</v>
+        <v>96410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2812</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rörbodarna, Jmt</t>
+          <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463285</v>
+        <v>463280</v>
       </c>
       <c r="R14" t="n">
-        <v>6992386</v>
+        <v>6992132</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1900,12 +2107,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1914,63 +2121,78 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130360389</v>
+        <v>131676384</v>
       </c>
       <c r="B15" t="n">
-        <v>80326</v>
+        <v>96410</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2812</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rörbodarna, Jmt</t>
+          <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463269</v>
+        <v>463144</v>
       </c>
       <c r="R15" t="n">
-        <v>6992434</v>
+        <v>6992354</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -1997,12 +2219,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2011,63 +2233,78 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130360383</v>
+        <v>131676385</v>
       </c>
       <c r="B16" t="n">
-        <v>79221</v>
+        <v>96410</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rörbodarna, Jmt</t>
+          <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462807</v>
+        <v>463135</v>
       </c>
       <c r="R16" t="n">
-        <v>6992456</v>
+        <v>6992481</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2094,12 +2331,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2108,63 +2345,81 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130360384</v>
+        <v>131676360</v>
       </c>
       <c r="B17" t="n">
-        <v>91734</v>
+        <v>92199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rörbodarna, Jmt</t>
+          <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463252</v>
+        <v>463127</v>
       </c>
       <c r="R17" t="n">
-        <v>6992494</v>
+        <v>6992488</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2191,12 +2446,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2205,50 +2460,76 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130360394</v>
+        <v>130360383</v>
       </c>
       <c r="B18" t="n">
-        <v>80326</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2539,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462876</v>
+        <v>462807</v>
       </c>
       <c r="R18" t="n">
-        <v>6992460</v>
+        <v>6992456</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2320,14 +2601,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131676392</v>
+        <v>131676390</v>
       </c>
       <c r="B19" t="n">
-        <v>79315</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2358,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463320</v>
+        <v>463273</v>
       </c>
       <c r="R19" t="n">
-        <v>6992152</v>
+        <v>6992528</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2394,11 +2675,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2446,14 +2722,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131676390</v>
+        <v>131676391</v>
       </c>
       <c r="B20" t="n">
-        <v>79315</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2484,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463273</v>
+        <v>463361</v>
       </c>
       <c r="R20" t="n">
-        <v>6992528</v>
+        <v>6992293</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2567,42 +2843,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131676363</v>
+        <v>131676392</v>
       </c>
       <c r="B21" t="n">
-        <v>57948</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2610,10 +2881,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463085</v>
+        <v>463320</v>
       </c>
       <c r="R21" t="n">
-        <v>6992732</v>
+        <v>6992152</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2650,7 +2921,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, långt upp på 2 granar vid en vändplan.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2659,6 +2930,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2677,14 +2949,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2702,41 +2969,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131676371</v>
+        <v>131676393</v>
       </c>
       <c r="B22" t="n">
-        <v>80420</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2744,10 +3007,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463360</v>
+        <v>463136</v>
       </c>
       <c r="R22" t="n">
-        <v>6992201</v>
+        <v>6992390</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2782,11 +3045,6 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2804,22 +3062,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -2837,32 +3090,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131676367</v>
+        <v>131703268</v>
       </c>
       <c r="B23" t="n">
-        <v>80324</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +3128,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463301</v>
+        <v>463276</v>
       </c>
       <c r="R23" t="n">
-        <v>6992616</v>
+        <v>6992513</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2913,11 +3166,6 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt på en asp.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2935,22 +3183,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -2968,10 +3211,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131676386</v>
+        <v>131703269</v>
       </c>
       <c r="B24" t="n">
-        <v>99095</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2979,54 +3222,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463294</v>
+        <v>463348</v>
       </c>
       <c r="R24" t="n">
-        <v>6992364</v>
+        <v>6992220</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3061,11 +3287,6 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,2 m2 yta i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3081,9 +3302,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Äldre klenvuxen granskog.</t>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3101,10 +3332,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131676372</v>
+        <v>130360397</v>
       </c>
       <c r="B25" t="n">
-        <v>80420</v>
+        <v>83307</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3112,37 +3343,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Röröbodarna, Jmt</t>
+          <t>Rörbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463338</v>
+        <v>463272</v>
       </c>
       <c r="R25" t="n">
-        <v>6992170</v>
+        <v>6992492</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3169,17 +3397,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På en sälghögstubbe.</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3188,54 +3411,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131676376</v>
+        <v>130360398</v>
       </c>
       <c r="B26" t="n">
-        <v>80420</v>
+        <v>83307</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3243,37 +3440,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Röröbodarna, Jmt</t>
+          <t>Rörbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>463071</v>
+        <v>463284</v>
       </c>
       <c r="R26" t="n">
-        <v>6992513</v>
+        <v>6992372</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3300,17 +3494,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en sälg.</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3319,54 +3508,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131676393</v>
+        <v>131703239</v>
       </c>
       <c r="B27" t="n">
-        <v>79315</v>
+        <v>83358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3374,21 +3537,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3401,10 +3564,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463136</v>
+        <v>463161</v>
       </c>
       <c r="R27" t="n">
-        <v>6992390</v>
+        <v>6992394</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3484,41 +3647,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131676374</v>
+        <v>131676367</v>
       </c>
       <c r="B28" t="n">
-        <v>80420</v>
+        <v>80382</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3526,10 +3685,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463152</v>
+        <v>463301</v>
       </c>
       <c r="R28" t="n">
-        <v>6992307</v>
+        <v>6992616</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3566,7 +3725,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Växer på en klen gran intill en grov gammal sälg med lunglav.</t>
+          <t>Rikligt på en asp.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3586,22 +3745,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3619,10 +3778,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131676366</v>
+        <v>130360389</v>
       </c>
       <c r="B29" t="n">
-        <v>58107</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3630,50 +3789,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Röröbodarna, Jmt</t>
+          <t>Rörbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463267</v>
+        <v>463269</v>
       </c>
       <c r="R29" t="n">
-        <v>6992176</v>
+        <v>6992434</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3700,17 +3843,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 2 talltitor i lämplig häckbiotop med flerskiktad granskog och murkna björkhögstubbar för bohål.</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3721,78 +3859,61 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Äldre granskog.</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131676378</v>
+        <v>130360390</v>
       </c>
       <c r="B30" t="n">
-        <v>80456</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Röröbodarna, Jmt</t>
+          <t>Rörbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463338</v>
+        <v>463285</v>
       </c>
       <c r="R30" t="n">
-        <v>6992275</v>
+        <v>6992386</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3819,17 +3940,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På en klen sälg.</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3838,54 +3954,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131676373</v>
+        <v>130360391</v>
       </c>
       <c r="B31" t="n">
-        <v>80420</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3911,23 +4001,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Röröbodarna, Jmt</t>
+          <t>Rörbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463208</v>
+        <v>463269</v>
       </c>
       <c r="R31" t="n">
-        <v>6992200</v>
+        <v>6992435</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3954,17 +4037,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Gott om bålar på en grovbarkad sälg.</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3973,96 +4051,63 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131676360</v>
+        <v>130360392</v>
       </c>
       <c r="B32" t="n">
-        <v>92612</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Röröbodarna, Jmt</t>
+          <t>Rörbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463127</v>
+        <v>463260</v>
       </c>
       <c r="R32" t="n">
-        <v>6992488</v>
+        <v>6992442</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4089,12 +4134,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4103,54 +4148,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131676362</v>
+        <v>130360393</v>
       </c>
       <c r="B33" t="n">
-        <v>57948</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4158,42 +4177,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Röröbodarna, Jmt</t>
+          <t>Rörbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463107</v>
+        <v>463223</v>
       </c>
       <c r="R33" t="n">
-        <v>6992727</v>
+        <v>6992479</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4220,17 +4231,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, enstaka kortare hålrad långt upp på en gran.</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4241,51 +4247,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131676368</v>
+        <v>130360394</v>
       </c>
       <c r="B34" t="n">
-        <v>80420</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4311,19 +4292,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Röröbodarna, Jmt</t>
+          <t>Rörbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463267</v>
+        <v>462876</v>
       </c>
       <c r="R34" t="n">
-        <v>6992432</v>
+        <v>6992460</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4350,12 +4328,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4364,54 +4342,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131676387</v>
+        <v>130360395</v>
       </c>
       <c r="B35" t="n">
-        <v>91909</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4419,37 +4371,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Röröbodarna, Jmt</t>
+          <t>Rörbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463366</v>
+        <v>462873</v>
       </c>
       <c r="R35" t="n">
-        <v>6992198</v>
+        <v>6992482</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4476,17 +4425,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4495,49 +4439,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131676389</v>
+        <v>131676368</v>
       </c>
       <c r="B36" t="n">
-        <v>91909</v>
+        <v>80488</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4545,26 +4468,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4572,10 +4495,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463146</v>
+        <v>463267</v>
       </c>
       <c r="R36" t="n">
-        <v>6992534</v>
+        <v>6992432</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4610,11 +4533,6 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och 28 cm i brösthöjdsdiameter. Högt livsmiljövärde för tretåig hackspett här här.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4632,22 +4550,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4668,7 +4586,7 @@
         <v>131676369</v>
       </c>
       <c r="B37" t="n">
-        <v>80420</v>
+        <v>80488</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4796,41 +4714,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131676377</v>
+        <v>131676370</v>
       </c>
       <c r="B38" t="n">
-        <v>80456</v>
+        <v>80488</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4838,10 +4752,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463266</v>
+        <v>463384</v>
       </c>
       <c r="R38" t="n">
-        <v>6992433</v>
+        <v>6992238</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4876,6 +4790,11 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en klen rönn i äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4893,12 +4812,12 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -4908,7 +4827,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4926,10 +4845,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131676388</v>
+        <v>131676371</v>
       </c>
       <c r="B39" t="n">
-        <v>91909</v>
+        <v>80488</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4937,24 +4856,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4964,10 +4887,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463270</v>
+        <v>463360</v>
       </c>
       <c r="R39" t="n">
-        <v>6992169</v>
+        <v>6992201</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5004,7 +4927,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Växer i en klen granhögstubbe.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5024,22 +4947,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5057,10 +4980,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131676375</v>
+        <v>131676372</v>
       </c>
       <c r="B40" t="n">
-        <v>80420</v>
+        <v>80488</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5087,11 +5010,7 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5099,10 +5018,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>463149</v>
+        <v>463338</v>
       </c>
       <c r="R40" t="n">
-        <v>6992304</v>
+        <v>6992170</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5139,7 +5058,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en grovbarkad gammal sälg med 61 cm i brösthöjdsdiameter.</t>
+          <t>På en sälghögstubbe.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5157,11 +5076,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>En sälg med 61 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AJ40" t="inlineStr">
         <is>
           <t>sälg</t>
@@ -5174,12 +5088,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5197,10 +5111,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131676391</v>
+        <v>131676373</v>
       </c>
       <c r="B41" t="n">
-        <v>79315</v>
+        <v>80488</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5208,26 +5122,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5235,10 +5153,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>463361</v>
+        <v>463208</v>
       </c>
       <c r="R41" t="n">
-        <v>6992293</v>
+        <v>6992200</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5273,6 +5191,11 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Gott om bålar på en grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5290,17 +5213,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5318,10 +5246,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131703248</v>
+        <v>131676374</v>
       </c>
       <c r="B42" t="n">
-        <v>80422</v>
+        <v>80488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5348,7 +5276,11 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5356,10 +5288,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>463293</v>
+        <v>463152</v>
       </c>
       <c r="R42" t="n">
-        <v>6992606</v>
+        <v>6992307</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5394,6 +5326,11 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Växer på en klen gran intill en grov gammal sälg med lunglav.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5406,27 +5343,27 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5444,10 +5381,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131703255</v>
+        <v>131676375</v>
       </c>
       <c r="B43" t="n">
-        <v>80422</v>
+        <v>80488</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5476,7 +5413,7 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5486,10 +5423,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>463239</v>
+        <v>463149</v>
       </c>
       <c r="R43" t="n">
-        <v>6992280</v>
+        <v>6992304</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5526,7 +5463,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på en sälg.</t>
+          <t>Rikligt med bålar på en grovbarkad gammal sälg med 61 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5544,6 +5481,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>En sälg med 61 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AJ43" t="inlineStr">
         <is>
           <t>sälg</t>
@@ -5561,7 +5503,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5579,10 +5521,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131703240</v>
+        <v>131676376</v>
       </c>
       <c r="B44" t="n">
-        <v>91892</v>
+        <v>80488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5590,30 +5532,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5621,10 +5559,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>463186</v>
+        <v>463071</v>
       </c>
       <c r="R44" t="n">
-        <v>6992482</v>
+        <v>6992513</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5659,6 +5597,11 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en sälg.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5676,22 +5619,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5709,65 +5652,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131703261</v>
+        <v>131703244</v>
       </c>
       <c r="B45" t="n">
-        <v>99098</v>
+        <v>80488</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>463156</v>
+        <v>463210</v>
       </c>
       <c r="R45" t="n">
-        <v>6992401</v>
+        <v>6992526</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5802,11 +5728,6 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 30 st plantor inom ca 1,5 m2 yta. Vid besöket på fyndplatsen var fortfarande stor del av marken snötäckt. Sannolikt finns betydligt fler plantor av knärot på och omkring fyndplatsen som blir synliga vid barmark.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5822,9 +5743,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog.</t>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5842,10 +5778,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131703266</v>
+        <v>131703245</v>
       </c>
       <c r="B46" t="n">
-        <v>91912</v>
+        <v>80488</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5853,26 +5789,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5880,10 +5816,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>463189</v>
+        <v>463272</v>
       </c>
       <c r="R46" t="n">
-        <v>6992483</v>
+        <v>6992608</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5935,17 +5871,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5963,10 +5904,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131703251</v>
+        <v>131703246</v>
       </c>
       <c r="B47" t="n">
-        <v>80422</v>
+        <v>80488</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5993,7 +5934,11 @@
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6001,10 +5946,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463327</v>
+        <v>463299</v>
       </c>
       <c r="R47" t="n">
-        <v>6992196</v>
+        <v>6992621</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6039,6 +5984,11 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglav på en sälg.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6051,7 +6001,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6089,10 +6039,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131703245</v>
+        <v>131703247</v>
       </c>
       <c r="B48" t="n">
-        <v>80422</v>
+        <v>80488</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6127,10 +6077,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>463272</v>
+        <v>463310</v>
       </c>
       <c r="R48" t="n">
-        <v>6992608</v>
+        <v>6992618</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6215,10 +6165,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131703267</v>
+        <v>131703248</v>
       </c>
       <c r="B49" t="n">
-        <v>91912</v>
+        <v>80488</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6226,26 +6176,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6253,10 +6203,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>463144</v>
+        <v>463293</v>
       </c>
       <c r="R49" t="n">
-        <v>6992498</v>
+        <v>6992606</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6291,11 +6241,6 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Fruktkroppar i en liggande död gran.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6308,27 +6253,27 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6346,10 +6291,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131703263</v>
+        <v>131703249</v>
       </c>
       <c r="B50" t="n">
-        <v>91888</v>
+        <v>80488</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6357,30 +6302,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6388,10 +6329,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>463359</v>
+        <v>463272</v>
       </c>
       <c r="R50" t="n">
-        <v>6992212</v>
+        <v>6992511</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6443,17 +6384,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6471,10 +6417,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131703247</v>
+        <v>131703250</v>
       </c>
       <c r="B51" t="n">
-        <v>80422</v>
+        <v>80488</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6501,7 +6447,11 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6509,10 +6459,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>463310</v>
+        <v>463346</v>
       </c>
       <c r="R51" t="n">
-        <v>6992618</v>
+        <v>6992274</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6547,6 +6497,11 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglavsbålar på en sälg.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6560,6 +6515,11 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -6597,10 +6557,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131703252</v>
+        <v>131703251</v>
       </c>
       <c r="B52" t="n">
-        <v>80422</v>
+        <v>80488</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6635,10 +6595,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>463321</v>
+        <v>463327</v>
       </c>
       <c r="R52" t="n">
-        <v>6992159</v>
+        <v>6992196</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6673,11 +6633,6 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På en björkhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6695,27 +6650,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>En björkhögstubbe.</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula # En björkhögstubbe.</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6733,10 +6683,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131703257</v>
+        <v>131703252</v>
       </c>
       <c r="B53" t="n">
-        <v>80422</v>
+        <v>80488</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6771,10 +6721,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>463179</v>
+        <v>463321</v>
       </c>
       <c r="R53" t="n">
-        <v>6992334</v>
+        <v>6992159</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6809,6 +6759,11 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På en björkhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6826,22 +6781,27 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>En björkhögstubbe.</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula # En björkhögstubbe.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6859,10 +6819,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131703268</v>
+        <v>131703253</v>
       </c>
       <c r="B54" t="n">
-        <v>79317</v>
+        <v>80488</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6870,21 +6830,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6897,10 +6857,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463276</v>
+        <v>463246</v>
       </c>
       <c r="R54" t="n">
-        <v>6992513</v>
+        <v>6992199</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6952,17 +6912,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6980,10 +6945,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131703239</v>
+        <v>131703254</v>
       </c>
       <c r="B55" t="n">
-        <v>83297</v>
+        <v>80488</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6991,21 +6956,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7018,10 +6983,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>463161</v>
+        <v>463261</v>
       </c>
       <c r="R55" t="n">
-        <v>6992394</v>
+        <v>6992247</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7073,17 +7038,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7101,10 +7071,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131703249</v>
+        <v>131703255</v>
       </c>
       <c r="B56" t="n">
-        <v>80422</v>
+        <v>80488</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7131,7 +7101,11 @@
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7139,10 +7113,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>463272</v>
+        <v>463239</v>
       </c>
       <c r="R56" t="n">
-        <v>6992511</v>
+        <v>6992280</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7175,6 +7149,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apothecier på en sälg.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7227,10 +7206,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131703269</v>
+        <v>131703256</v>
       </c>
       <c r="B57" t="n">
-        <v>79317</v>
+        <v>80488</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7238,21 +7217,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7265,10 +7244,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>463348</v>
+        <v>463198</v>
       </c>
       <c r="R57" t="n">
-        <v>6992220</v>
+        <v>6992263</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7320,17 +7299,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7348,10 +7332,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131703260</v>
+        <v>131703257</v>
       </c>
       <c r="B58" t="n">
-        <v>78329</v>
+        <v>80488</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7359,21 +7343,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7386,10 +7370,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>463236</v>
+        <v>463179</v>
       </c>
       <c r="R58" t="n">
-        <v>6992549</v>
+        <v>6992334</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7441,17 +7425,22 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7469,10 +7458,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131703243</v>
+        <v>131703258</v>
       </c>
       <c r="B59" t="n">
-        <v>58109</v>
+        <v>80488</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7480,50 +7469,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>463141</v>
+        <v>463161</v>
       </c>
       <c r="R59" t="n">
-        <v>6992529</v>
+        <v>6992400</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7564,6 +7540,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7572,9 +7549,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7592,10 +7584,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131703262</v>
+        <v>131703259</v>
       </c>
       <c r="B60" t="n">
-        <v>91888</v>
+        <v>80488</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7603,30 +7595,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7634,10 +7622,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>463229</v>
+        <v>463200</v>
       </c>
       <c r="R60" t="n">
-        <v>6992394</v>
+        <v>6992327</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7672,6 +7660,11 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Växer här på en död sälg.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7689,17 +7682,22 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7717,39 +7715,39 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131703264</v>
+        <v>131676377</v>
       </c>
       <c r="B61" t="n">
-        <v>91888</v>
+        <v>80500</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7759,10 +7757,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>463196</v>
+        <v>463266</v>
       </c>
       <c r="R61" t="n">
-        <v>6992334</v>
+        <v>6992433</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7814,17 +7812,22 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7842,37 +7845,41 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131703253</v>
+        <v>131676378</v>
       </c>
       <c r="B62" t="n">
-        <v>80422</v>
+        <v>80500</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7880,10 +7887,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>463246</v>
+        <v>463338</v>
       </c>
       <c r="R62" t="n">
-        <v>6992199</v>
+        <v>6992275</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7916,6 +7923,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På en klen sälg.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7968,10 +7980,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131703256</v>
+        <v>131676362</v>
       </c>
       <c r="B63" t="n">
-        <v>80422</v>
+        <v>57975</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7979,26 +7991,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8006,10 +8023,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>463198</v>
+        <v>463107</v>
       </c>
       <c r="R63" t="n">
-        <v>6992263</v>
+        <v>6992727</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8044,13 +8061,17 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, enstaka kortare hålrad långt upp på en gran.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8061,22 +8082,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8094,10 +8115,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131703246</v>
+        <v>131676363</v>
       </c>
       <c r="B64" t="n">
-        <v>80422</v>
+        <v>57975</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8105,28 +8126,29 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8136,10 +8158,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>463299</v>
+        <v>463085</v>
       </c>
       <c r="R64" t="n">
-        <v>6992621</v>
+        <v>6992732</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8176,7 +8198,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en sälg.</t>
+          <t>Ringhack (savhack), färska, långt upp på 2 granar vid en vändplan.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8185,33 +8207,32 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8229,10 +8250,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131703254</v>
+        <v>131676364</v>
       </c>
       <c r="B65" t="n">
-        <v>80422</v>
+        <v>57975</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8240,37 +8261,54 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>463261</v>
+        <v>463385</v>
       </c>
       <c r="R65" t="n">
-        <v>6992247</v>
+        <v>6992212</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8305,13 +8343,17 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>1 hona som födosökte långt upp på en stående död gran med ca 10 cm i brösthöjdsdiameter. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på stående död ved av gran.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8320,24 +8362,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad bilvis flerskiktad skog med många partier med högt och mycket högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8355,10 +8382,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131703259</v>
+        <v>131676366</v>
       </c>
       <c r="B66" t="n">
-        <v>80422</v>
+        <v>58136</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8366,37 +8393,50 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>463200</v>
+        <v>463267</v>
       </c>
       <c r="R66" t="n">
-        <v>6992327</v>
+        <v>6992176</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8433,7 +8473,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Växer här på en död sälg.</t>
+          <t>Minst 2 talltitor i lämplig häckbiotop med flerskiktad granskog och murkna björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8442,7 +8482,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8451,24 +8490,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8486,10 +8510,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131703250</v>
+        <v>131703243</v>
       </c>
       <c r="B67" t="n">
-        <v>80422</v>
+        <v>58136</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8497,41 +8521,50 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>463346</v>
+        <v>463141</v>
       </c>
       <c r="R67" t="n">
-        <v>6992274</v>
+        <v>6992529</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8566,18 +8599,12 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglavsbålar på en sälg.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8588,27 +8615,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Äldre granskog.</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bitvis flerskiktad äldre granskog med inslag av murkna björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8626,48 +8633,61 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131703244</v>
+        <v>131676365</v>
       </c>
       <c r="B68" t="n">
-        <v>80422</v>
+        <v>58131</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>103023</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>463210</v>
+        <v>463276</v>
       </c>
       <c r="R68" t="n">
-        <v>6992526</v>
+        <v>6992173</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8702,13 +8722,17 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>En tofsmes med lockläte som hängde med två talltitor.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8717,24 +8741,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Äldre bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8752,37 +8761,42 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131703270</v>
+        <v>131676379</v>
       </c>
       <c r="B69" t="n">
-        <v>83163</v>
+        <v>111153</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>220240</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8790,10 +8804,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>463157</v>
+        <v>463288</v>
       </c>
       <c r="R69" t="n">
-        <v>6992429</v>
+        <v>6992634</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8840,27 +8854,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog.</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8878,37 +8872,42 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131703258</v>
+        <v>131676380</v>
       </c>
       <c r="B70" t="n">
-        <v>80422</v>
+        <v>111153</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220240</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8916,10 +8915,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>463161</v>
+        <v>463298</v>
       </c>
       <c r="R70" t="n">
-        <v>6992400</v>
+        <v>6992368</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8969,24 +8968,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9004,65 +8988,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131676364</v>
+        <v>130360386</v>
       </c>
       <c r="B71" t="n">
-        <v>57948</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Röröbodarna, Jmt</t>
+          <t>Rörbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>463385</v>
+        <v>463100</v>
       </c>
       <c r="R71" t="n">
-        <v>6992212</v>
+        <v>6992447</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9089,17 +9053,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>1 hona som födosökte långt upp på en stående död gran med ca 10 cm i brösthöjdsdiameter. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på stående död ved av gran.</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9110,74 +9069,81 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad bilvis flerskiktad skog med många partier med högt och mycket högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved.</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131676370</v>
+        <v>131676386</v>
       </c>
       <c r="B72" t="n">
-        <v>80420</v>
+        <v>99195</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>463384</v>
+        <v>463294</v>
       </c>
       <c r="R72" t="n">
-        <v>6992238</v>
+        <v>6992364</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9214,7 +9180,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en klen rönn i äldre granskog.</t>
+          <t>Minst 12 plantor inom ca 0,2 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9232,24 +9198,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Äldre klenvuxen granskog.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9267,52 +9218,65 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131703265</v>
+        <v>131703261</v>
       </c>
       <c r="B73" t="n">
-        <v>91888</v>
+        <v>99195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Röröbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>463389</v>
+        <v>463156</v>
       </c>
       <c r="R73" t="n">
-        <v>6992233</v>
+        <v>6992401</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9347,6 +9311,11 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Minst 30 st plantor inom ca 1,5 m2 yta. Vid besöket på fyndplatsen var fortfarande stor del av marken snötäckt. Sannolikt finns betydligt fler plantor av knärot på och omkring fyndplatsen som blir synliga vid barmark.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9362,19 +9331,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog.</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9389,6 +9348,335 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>117778014</v>
+      </c>
+      <c r="B74" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Röröbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>463370</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6992549</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>130360388</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Rörbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>463285</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6992372</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>131703260</v>
+      </c>
+      <c r="B76" t="n">
+        <v>78382</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Röröbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>463236</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6992549</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63339-2025 artfynd.xlsx
+++ b/artfynd/A 63339-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AZ76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130360399</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130360384</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703262</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703263</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703264</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1366,6 +1396,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703265</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130360385</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1593,6 +1633,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703240</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1719,6 +1764,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703270</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1816,6 +1866,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130360382</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1923,6 +1978,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676381</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2035,6 +2095,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676382</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2147,6 +2212,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676383</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2259,6 +2329,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676384</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2371,6 +2446,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676385</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2501,6 +2581,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676360</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2598,6 +2683,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130360383</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2719,6 +2809,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676390</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2840,6 +2935,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676391</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2966,6 +3066,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676392</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3087,6 +3192,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676393</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3208,6 +3318,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703268</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3329,6 +3444,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703269</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3426,6 +3546,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130360397</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3523,6 +3648,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130360398</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3644,6 +3774,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703239</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3775,6 +3910,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676367</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3872,6 +4012,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130360389</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3969,6 +4114,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130360390</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4066,6 +4216,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130360391</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4163,6 +4318,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130360392</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4260,6 +4420,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130360393</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4357,6 +4522,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130360394</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4454,6 +4624,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130360395</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4580,6 +4755,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676368</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4711,6 +4891,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676369</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4842,6 +5027,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676370</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4977,6 +5167,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676371</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5108,6 +5303,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676372</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5243,6 +5443,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676373</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5378,6 +5583,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676374</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5518,6 +5728,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676375</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5649,6 +5864,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676376</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5775,6 +5995,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703244</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5901,6 +6126,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703245</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6036,6 +6266,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703246</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6162,6 +6397,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703247</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6288,6 +6528,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703248</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6414,6 +6659,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703249</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6554,6 +6804,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703250</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6680,6 +6935,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703251</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6816,6 +7076,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703252</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6942,6 +7207,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703253</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7068,6 +7338,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703254</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7203,6 +7478,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703255</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7329,6 +7609,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703256</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7455,6 +7740,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703257</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7581,6 +7871,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703258</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7712,6 +8007,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703259</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7842,6 +8142,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676377</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7977,6 +8282,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676378</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8112,6 +8422,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676362</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8247,6 +8562,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676363</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8379,6 +8699,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676364</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8507,6 +8832,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676366</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8630,6 +8960,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703243</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8758,6 +9093,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676365</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8869,6 +9209,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676379</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8985,6 +9330,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676380</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9082,6 +9432,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130360386</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9215,6 +9570,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131676386</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9348,6 +9708,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703261</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9459,6 +9824,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117778014</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9556,6 +9926,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130360388</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9677,8 +10052,90 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131703260</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>